--- a/output/roomself_excel/10173.xlsx
+++ b/output/roomself_excel/10173.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>197980</v>
+        <v>92961</v>
       </c>
       <c r="D2" t="n">
-        <v>3604</v>
+        <v>2692</v>
       </c>
       <c r="E2" t="n">
-        <v>708</v>
+        <v>304</v>
       </c>
       <c r="F2" t="n">
-        <v>564</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22288</v>
+        <v>68239</v>
       </c>
       <c r="D3" t="n">
-        <v>2044</v>
+        <v>2368</v>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>124389</v>
+        <v>197980</v>
       </c>
       <c r="D4" t="n">
-        <v>2920</v>
+        <v>3604</v>
       </c>
       <c r="E4" t="n">
-        <v>271</v>
+        <v>564</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>91593</v>
+        <v>22288</v>
       </c>
       <c r="D5" t="n">
-        <v>2840</v>
+        <v>2044</v>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>228</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90831</v>
+        <v>124389</v>
       </c>
       <c r="D6" t="n">
-        <v>2608</v>
+        <v>2920</v>
       </c>
       <c r="E6" t="n">
-        <v>383</v>
+        <v>271</v>
       </c>
       <c r="F6" t="n">
-        <v>277</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>68239</v>
+        <v>91593</v>
       </c>
       <c r="D7" t="n">
-        <v>2368</v>
+        <v>2840</v>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>510</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3780</v>
+        <v>90831</v>
       </c>
       <c r="D8" t="n">
-        <v>496</v>
+        <v>2608</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>372</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6890</v>
+        <v>3780</v>
       </c>
       <c r="D9" t="n">
-        <v>732</v>
+        <v>496</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8094</v>
+        <v>6890</v>
       </c>
       <c r="D10" t="n">
-        <v>796</v>
+        <v>732</v>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>92961</v>
+        <v>8094</v>
       </c>
       <c r="D11" t="n">
-        <v>2692</v>
+        <v>796</v>
       </c>
       <c r="E11" t="n">
-        <v>585</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>304</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">

--- a/output/roomself_excel/10173.xlsx
+++ b/output/roomself_excel/10173.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2692</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>304</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>41</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>297</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +533,20 @@
       <c r="D3" t="n">
         <v>2368</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>112</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>22</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>3604</v>
       </c>
-      <c r="E4" t="n">
-        <v>564</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>421</v>
+        <v>521</v>
+      </c>
+      <c r="G4" t="n">
+        <v>41</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>380</v>
+      </c>
+      <c r="J4" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +601,20 @@
       <c r="D5" t="n">
         <v>2044</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>52</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>41</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +631,20 @@
       <c r="D6" t="n">
         <v>2920</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>271</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>41</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +661,27 @@
       <c r="D7" t="n">
         <v>2840</v>
       </c>
-      <c r="E7" t="n">
-        <v>510</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>228</v>
+        <v>187</v>
+      </c>
+      <c r="G7" t="n">
+        <v>41</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>459</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -607,11 +699,27 @@
       <c r="D8" t="n">
         <v>2608</v>
       </c>
-      <c r="E8" t="n">
-        <v>372</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>277</v>
+        <v>255</v>
+      </c>
+      <c r="G8" t="n">
+        <v>43</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>329</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +737,20 @@
       <c r="D9" t="n">
         <v>496</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>54</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>41</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +767,12 @@
       <c r="D10" t="n">
         <v>732</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +789,20 @@
       <c r="D11" t="n">
         <v>796</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>57</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>22</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +819,27 @@
       <c r="D12" t="n">
         <v>1420</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>147</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>29</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>196</v>
+      </c>
+      <c r="J12" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
